--- a/src/width_txt/Максимальные_значения_определителя_АЦП_№2.xlsx
+++ b/src/width_txt/Максимальные_значения_определителя_АЦП_№2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="430" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="602" uniqueCount="43">
   <si>
     <t>Row</t>
   </si>
@@ -202,7 +202,7 @@
     <col min="10" max="10" width="15.85546875" customWidth="true"/>
     <col min="11" max="11" width="15.85546875" customWidth="true"/>
     <col min="12" max="12" width="15.85546875" customWidth="true"/>
-    <col min="13" max="13" width="15.85546875" customWidth="true"/>
+    <col min="13" max="13" width="14.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -251,40 +251,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C2" s="0">
-        <v>2191044053340</v>
+        <v>36312676120</v>
       </c>
       <c r="D2" s="0">
-        <v>5371778016718464</v>
+        <v>52580755021760</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>7773244880514534</v>
+        <v>40411616447</v>
       </c>
       <c r="G2" s="0">
-        <v>2.0046431986338505e+19</v>
+        <v>58516020615256</v>
       </c>
       <c r="H2" s="0">
-        <v>1.8017740482752145e+19</v>
+        <v>45981168099407</v>
       </c>
       <c r="I2" s="0">
-        <v>3.6567451494551708e+19</v>
+        <v>90879168380</v>
       </c>
       <c r="J2" s="0">
-        <v>9.0820780622104331e+22</v>
+        <v>131593035814240</v>
       </c>
       <c r="K2" s="0">
-        <v>1.0186117499389792e+23</v>
+        <v>131849089058335</v>
       </c>
       <c r="L2" s="0">
-        <v>1.1464911759391607e+23</v>
+        <v>111075088424080</v>
       </c>
       <c r="M2" s="0">
-        <v>1.7331784076700777e+23</v>
+        <v>106680142983</v>
       </c>
     </row>
     <row r="3">
@@ -292,34 +292,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>1747792316969</v>
+        <v>209709789944</v>
       </c>
       <c r="C3" s="0">
-        <v>2332107064774</v>
+        <v>36312676120</v>
       </c>
       <c r="D3" s="0">
-        <v>5371778016718464</v>
+        <v>52580755021760</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>7773244880514534</v>
+        <v>40411616447</v>
       </c>
       <c r="G3" s="0">
-        <v>1.4961582028453659e+19</v>
+        <v>58516020615256</v>
       </c>
       <c r="H3" s="0">
-        <v>2.6253069814888579e+19</v>
+        <v>58430689177408</v>
       </c>
       <c r="I3" s="0">
-        <v>3.0977047416703488e+19</v>
+        <v>90879168380</v>
       </c>
       <c r="J3" s="0">
-        <v>8.8749592983829609e+22</v>
+        <v>131593035814240</v>
       </c>
       <c r="K3" s="0">
-        <v>9.2333397752914085e+22</v>
+        <v>112786338717752</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -333,31 +333,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C4" s="0">
-        <v>2541451632035</v>
+        <v>36312676120</v>
       </c>
       <c r="D4" s="0">
-        <v>5371778016718464</v>
+        <v>52580755021760</v>
       </c>
       <c r="E4" s="0">
         <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>7755864712153196</v>
+        <v>28055377973</v>
       </c>
       <c r="G4" s="0">
-        <v>1.9312709081912197e+19</v>
+        <v>40624187304904</v>
       </c>
       <c r="H4" s="0">
-        <v>1.8017740482752145e+19</v>
+        <v>58414510398288</v>
       </c>
       <c r="I4" s="0">
-        <v>2.4672574322105016e+19</v>
+        <v>35982442344</v>
       </c>
       <c r="J4" s="0">
-        <v>6.089507442430091e+22</v>
+        <v>52102576514112</v>
       </c>
       <c r="K4" s="0">
         <v>0</v>
@@ -374,31 +374,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>1706993451008</v>
+        <v>209709789944</v>
       </c>
       <c r="C5" s="0">
-        <v>2541451632035</v>
+        <v>36312676120</v>
       </c>
       <c r="D5" s="0">
-        <v>4751720146708992</v>
+        <v>52580755021760</v>
       </c>
       <c r="E5" s="0">
         <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>7429655348911839</v>
+        <v>33932898236</v>
       </c>
       <c r="G5" s="0">
-        <v>2.271012921871283e+19</v>
+        <v>49134836645728</v>
       </c>
       <c r="H5" s="0">
-        <v>2.4070632451540165e+19</v>
+        <v>58430689177408</v>
       </c>
       <c r="I5" s="0">
-        <v>2.9979386560510575e+19</v>
+        <v>64155384920</v>
       </c>
       <c r="J5" s="0">
-        <v>8.0146563736650702e+22</v>
+        <v>92961152749080</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -415,31 +415,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C6" s="0">
-        <v>2332107064774</v>
+        <v>36312676120</v>
       </c>
       <c r="D6" s="0">
-        <v>4773823161592378</v>
+        <v>52580755021760</v>
       </c>
       <c r="E6" s="0">
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>7773244880514534</v>
+        <v>40411616447</v>
       </c>
       <c r="G6" s="0">
-        <v>2.0046431986338505e+19</v>
+        <v>58516020615256</v>
       </c>
       <c r="H6" s="0">
-        <v>1.6277661154461288e+19</v>
+        <v>58414510398288</v>
       </c>
       <c r="I6" s="0">
-        <v>3.6567451494551708e+19</v>
+        <v>76709315210</v>
       </c>
       <c r="J6" s="0">
-        <v>9.7320925933791961e+22</v>
+        <v>111151797739290</v>
       </c>
       <c r="K6" s="0">
         <v>0</v>
@@ -456,25 +456,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C7" s="0">
-        <v>2541451632035</v>
+        <v>36312676120</v>
       </c>
       <c r="D7" s="0">
-        <v>4773823161592378</v>
+        <v>52580755021760</v>
       </c>
       <c r="E7" s="0">
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>7755864712153196</v>
+        <v>28055377973</v>
       </c>
       <c r="G7" s="0">
-        <v>1.7380061550276891e+19</v>
+        <v>58516020615256</v>
       </c>
       <c r="H7" s="0">
-        <v>1.8705370885500289e+19</v>
+        <v>45774463850816</v>
       </c>
       <c r="I7" s="0">
         <v>0</v>
@@ -497,25 +497,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>1852829188699</v>
+        <v>209709789944</v>
       </c>
       <c r="C8" s="0">
-        <v>2541451632035</v>
+        <v>36312676120</v>
       </c>
       <c r="D8" s="0">
-        <v>5383133133871104</v>
+        <v>52580755021760</v>
       </c>
       <c r="E8" s="0">
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>7429655348911839</v>
+        <v>33932898236</v>
       </c>
       <c r="G8" s="0">
-        <v>1.7644693240403433e+19</v>
+        <v>40624187304904</v>
       </c>
       <c r="H8" s="0">
-        <v>1.942624803395722e+19</v>
+        <v>40624187304904</v>
       </c>
       <c r="I8" s="0">
         <v>0</v>
@@ -538,25 +538,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C9" s="0">
-        <v>2541451632035</v>
+        <v>36312676120</v>
       </c>
       <c r="D9" s="0">
-        <v>5383133133871104</v>
+        <v>52580755021760</v>
       </c>
       <c r="E9" s="0">
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>7810160212129588</v>
+        <v>26202223184</v>
       </c>
       <c r="G9" s="0">
-        <v>2.2512461275919557e+19</v>
+        <v>49134836645728</v>
       </c>
       <c r="H9" s="0">
-        <v>2.823124165136828e+19</v>
+        <v>37940819170432</v>
       </c>
       <c r="I9" s="0">
         <v>0</v>
@@ -579,25 +579,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C10" s="0">
-        <v>2541451632035</v>
+        <v>36312676120</v>
       </c>
       <c r="D10" s="0">
-        <v>5383133133871104</v>
+        <v>52580755021760</v>
       </c>
       <c r="E10" s="0">
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>7810160212129588</v>
+        <v>24271853062</v>
       </c>
       <c r="G10" s="0">
-        <v>1.5919605515293766e+19</v>
+        <v>58516020615256</v>
       </c>
       <c r="H10" s="0">
-        <v>2.4093856728877576e+19</v>
+        <v>49049505207880</v>
       </c>
       <c r="I10" s="0">
         <v>0</v>
@@ -620,25 +620,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C11" s="0">
-        <v>2541451632035</v>
+        <v>36312676120</v>
       </c>
       <c r="D11" s="0">
-        <v>5797257484752384</v>
+        <v>52580755021760</v>
       </c>
       <c r="E11" s="0">
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>7810160212129588</v>
+        <v>28055377973</v>
       </c>
       <c r="G11" s="0">
-        <v>1.7380061550276891e+19</v>
+        <v>58516020615256</v>
       </c>
       <c r="H11" s="0">
-        <v>2.823124165136828e+19</v>
+        <v>38753322359608</v>
       </c>
       <c r="I11" s="0">
         <v>0</v>
@@ -661,13 +661,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C12" s="0">
         <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>5797257484752384</v>
+        <v>52580755021760</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>1.7547197535292584e+19</v>
+        <v>37940819170432</v>
       </c>
       <c r="H12" s="0">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C13" s="0">
         <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>5797257484752384</v>
+        <v>52580755021760</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>1.5815829580681771e+19</v>
+        <v>35145643233776</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1852829188699</v>
+        <v>209709789944</v>
       </c>
       <c r="C14" s="0">
         <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>5184162109757657</v>
+        <v>52580755021760</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <v>1.9312709081912197e+19</v>
+        <v>40624187304904</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C15" s="0">
         <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>5184162109757657</v>
+        <v>52580755021760</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>1.7644693240403433e+19</v>
+        <v>40624187304904</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C16" s="0">
         <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>5184162109757657</v>
+        <v>52580755021760</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>1.7547197535292584e+19</v>
+        <v>37940819170432</v>
       </c>
       <c r="H16" s="0">
         <v>0</v>
@@ -866,13 +866,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C17" s="0">
         <v>0</v>
       </c>
       <c r="D17" s="0">
-        <v>5316143240114685</v>
+        <v>52580755021760</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="0">
-        <v>1.6620630027468282e+19</v>
+        <v>40652242682877</v>
       </c>
       <c r="H17" s="0">
         <v>0</v>
@@ -907,13 +907,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1852829188699</v>
+        <v>209709789944</v>
       </c>
       <c r="C18" s="0">
         <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>5316143240114685</v>
+        <v>52580755021760</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>2.271012921871283e+19</v>
+        <v>49134836645728</v>
       </c>
       <c r="H18" s="0">
         <v>0</v>
@@ -948,13 +948,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C19" s="0">
         <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>5316143240114685</v>
+        <v>52580755021760</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>2.2512461275919557e+19</v>
+        <v>49134836645728</v>
       </c>
       <c r="H19" s="0">
         <v>0</v>
@@ -989,13 +989,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C20" s="0">
         <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>4884379363847992</v>
+        <v>52580755021760</v>
       </c>
       <c r="E20" s="0">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <v>1.5987397954229266e+19</v>
+        <v>35145643233776</v>
       </c>
       <c r="H20" s="0">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>1989081674344</v>
+        <v>209709789944</v>
       </c>
       <c r="C21" s="0">
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>4884379363847992</v>
+        <v>52580755021760</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>1.6620630027468282e+19</v>
+        <v>40624187304904</v>
       </c>
       <c r="H21" s="0">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>4884379363847992</v>
+        <v>52580755021760</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="0">
-        <v>6486754989635199</v>
+        <v>52580755021760</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>6486754989635199</v>
+        <v>52580755021760</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>6486754989635199</v>
+        <v>52580755021760</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>6486754989635199</v>
+        <v>52580755021760</v>
       </c>
       <c r="E26" s="0">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>6486754989635199</v>
+        <v>52580755021760</v>
       </c>
       <c r="E27" s="0">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>6486754989635199</v>
+        <v>52580755021760</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>5857903607043308</v>
+        <v>52580755021760</v>
       </c>
       <c r="E29" s="0">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>5857903607043308</v>
+        <v>52580755021760</v>
       </c>
       <c r="E30" s="0">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>5857903607043308</v>
+        <v>52580755021760</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>

--- a/src/width_txt/Максимальные_значения_определителя_АЦП_№2.xlsx
+++ b/src/width_txt/Максимальные_значения_определителя_АЦП_№2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="602" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2795" uniqueCount="43">
   <si>
     <t>Row</t>
   </si>
@@ -191,18 +191,18 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true"/>
-    <col min="2" max="2" width="15.85546875" customWidth="true"/>
-    <col min="3" max="3" width="15.85546875" customWidth="true"/>
-    <col min="4" max="4" width="15.85546875" customWidth="true"/>
+    <col min="2" max="2" width="14.85546875" customWidth="true"/>
+    <col min="3" max="3" width="11.42578125" customWidth="true"/>
+    <col min="4" max="4" width="14.85546875" customWidth="true"/>
     <col min="5" max="5" width="12.85546875" customWidth="true"/>
-    <col min="6" max="6" width="15.85546875" customWidth="true"/>
+    <col min="6" max="6" width="10.140625" customWidth="true"/>
     <col min="7" max="7" width="15.85546875" customWidth="true"/>
     <col min="8" max="8" width="15.85546875" customWidth="true"/>
-    <col min="9" max="9" width="15.85546875" customWidth="true"/>
+    <col min="9" max="9" width="11.140625" customWidth="true"/>
     <col min="10" max="10" width="15.85546875" customWidth="true"/>
     <col min="11" max="11" width="15.85546875" customWidth="true"/>
     <col min="12" max="12" width="15.85546875" customWidth="true"/>
-    <col min="13" max="13" width="14.85546875" customWidth="true"/>
+    <col min="13" max="13" width="15.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -251,40 +251,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>209709789944</v>
+        <v>3854148</v>
       </c>
       <c r="C2" s="0">
-        <v>36312676120</v>
+        <v>1543274</v>
       </c>
       <c r="D2" s="0">
-        <v>52580755021760</v>
+        <v>3122043302</v>
       </c>
       <c r="E2" s="0">
-        <v>0</v>
+        <v>1208368374</v>
       </c>
       <c r="F2" s="0">
-        <v>40411616447</v>
+        <v>292958157</v>
       </c>
       <c r="G2" s="0">
-        <v>58516020615256</v>
+        <v>144710398080</v>
       </c>
       <c r="H2" s="0">
-        <v>45981168099407</v>
+        <v>362822543892</v>
       </c>
       <c r="I2" s="0">
-        <v>90879168380</v>
+        <v>5786336799</v>
       </c>
       <c r="J2" s="0">
-        <v>131593035814240</v>
+        <v>10536919310979</v>
       </c>
       <c r="K2" s="0">
-        <v>131849089058335</v>
+        <v>4004389109943</v>
       </c>
       <c r="L2" s="0">
-        <v>111075088424080</v>
+        <v>7730418917352</v>
       </c>
       <c r="M2" s="0">
-        <v>106680142983</v>
+        <v>67035140184</v>
       </c>
     </row>
     <row r="3">
@@ -292,34 +292,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>209709789944</v>
+        <v>4182025</v>
       </c>
       <c r="C3" s="0">
-        <v>36312676120</v>
+        <v>2418546</v>
       </c>
       <c r="D3" s="0">
-        <v>52580755021760</v>
+        <v>2818018324</v>
       </c>
       <c r="E3" s="0">
-        <v>0</v>
+        <v>1643969746</v>
       </c>
       <c r="F3" s="0">
-        <v>40411616447</v>
+        <v>292648410</v>
       </c>
       <c r="G3" s="0">
-        <v>58516020615256</v>
+        <v>414840984201</v>
       </c>
       <c r="H3" s="0">
-        <v>58430689177408</v>
+        <v>366065603685</v>
       </c>
       <c r="I3" s="0">
-        <v>90879168380</v>
+        <v>7031787084</v>
       </c>
       <c r="J3" s="0">
-        <v>131593035814240</v>
+        <v>6532530201036</v>
       </c>
       <c r="K3" s="0">
-        <v>112786338717752</v>
+        <v>8688948778308</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -333,31 +333,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>209709789944</v>
+        <v>3854148</v>
       </c>
       <c r="C4" s="0">
-        <v>36312676120</v>
+        <v>2360770</v>
       </c>
       <c r="D4" s="0">
-        <v>52580755021760</v>
+        <v>1433701546</v>
       </c>
       <c r="E4" s="0">
-        <v>0</v>
+        <v>1930090168</v>
       </c>
       <c r="F4" s="0">
-        <v>28055377973</v>
+        <v>281115459</v>
       </c>
       <c r="G4" s="0">
-        <v>40624187304904</v>
+        <v>568977689016</v>
       </c>
       <c r="H4" s="0">
-        <v>58414510398288</v>
+        <v>574951688289</v>
       </c>
       <c r="I4" s="0">
-        <v>35982442344</v>
+        <v>4658454960</v>
       </c>
       <c r="J4" s="0">
-        <v>52102576514112</v>
+        <v>1486047132240</v>
       </c>
       <c r="K4" s="0">
         <v>0</v>
@@ -374,31 +374,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>209709789944</v>
+        <v>4075736</v>
       </c>
       <c r="C5" s="0">
-        <v>36312676120</v>
+        <v>1502601</v>
       </c>
       <c r="D5" s="0">
-        <v>52580755021760</v>
+        <v>3499636062</v>
       </c>
       <c r="E5" s="0">
-        <v>0</v>
+        <v>1643969746</v>
       </c>
       <c r="F5" s="0">
-        <v>33932898236</v>
+        <v>292958157</v>
       </c>
       <c r="G5" s="0">
-        <v>49134836645728</v>
+        <v>524070020124</v>
       </c>
       <c r="H5" s="0">
-        <v>58430689177408</v>
+        <v>578804185353</v>
       </c>
       <c r="I5" s="0">
-        <v>64155384920</v>
+        <v>7031787084</v>
       </c>
       <c r="J5" s="0">
-        <v>92961152749080</v>
+        <v>10174995910548</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -415,31 +415,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>209709789944</v>
+        <v>3854148</v>
       </c>
       <c r="C6" s="0">
-        <v>36312676120</v>
+        <v>2418546</v>
       </c>
       <c r="D6" s="0">
-        <v>52580755021760</v>
+        <v>4416264996</v>
       </c>
       <c r="E6" s="0">
-        <v>0</v>
+        <v>1930090168</v>
       </c>
       <c r="F6" s="0">
-        <v>40411616447</v>
+        <v>292958157</v>
       </c>
       <c r="G6" s="0">
-        <v>58516020615256</v>
+        <v>251085152637</v>
       </c>
       <c r="H6" s="0">
-        <v>58414510398288</v>
+        <v>359690208597</v>
       </c>
       <c r="I6" s="0">
-        <v>76709315210</v>
+        <v>3852497064</v>
       </c>
       <c r="J6" s="0">
-        <v>111151797739290</v>
+        <v>7797454057536</v>
       </c>
       <c r="K6" s="0">
         <v>0</v>
@@ -456,25 +456,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>209709789944</v>
+        <v>3871920</v>
       </c>
       <c r="C7" s="0">
-        <v>36312676120</v>
+        <v>2360770</v>
       </c>
       <c r="D7" s="0">
-        <v>52580755021760</v>
+        <v>2246829234</v>
       </c>
       <c r="E7" s="0">
-        <v>0</v>
+        <v>1930090168</v>
       </c>
       <c r="F7" s="0">
-        <v>28055377973</v>
+        <v>292648410</v>
       </c>
       <c r="G7" s="0">
-        <v>58516020615256</v>
+        <v>423462249270</v>
       </c>
       <c r="H7" s="0">
-        <v>45774463850816</v>
+        <v>360643174959</v>
       </c>
       <c r="I7" s="0">
         <v>0</v>
@@ -497,25 +497,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>209709789944</v>
+        <v>3854148</v>
       </c>
       <c r="C8" s="0">
-        <v>36312676120</v>
+        <v>2358879</v>
       </c>
       <c r="D8" s="0">
-        <v>52580755021760</v>
+        <v>3416034190</v>
       </c>
       <c r="E8" s="0">
-        <v>0</v>
+        <v>3624255940</v>
       </c>
       <c r="F8" s="0">
-        <v>33932898236</v>
+        <v>286690383</v>
       </c>
       <c r="G8" s="0">
-        <v>40624187304904</v>
+        <v>592947309768</v>
       </c>
       <c r="H8" s="0">
-        <v>40624187304904</v>
+        <v>318548063406</v>
       </c>
       <c r="I8" s="0">
         <v>0</v>
@@ -538,25 +538,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>209709789944</v>
+        <v>3871920</v>
       </c>
       <c r="C9" s="0">
-        <v>36312676120</v>
+        <v>2418546</v>
       </c>
       <c r="D9" s="0">
-        <v>52580755021760</v>
+        <v>4777929288</v>
       </c>
       <c r="E9" s="0">
-        <v>0</v>
+        <v>3622531998</v>
       </c>
       <c r="F9" s="0">
-        <v>26202223184</v>
+        <v>281115459</v>
       </c>
       <c r="G9" s="0">
-        <v>49134836645728</v>
+        <v>535527510996</v>
       </c>
       <c r="H9" s="0">
-        <v>37940819170432</v>
+        <v>322010152443</v>
       </c>
       <c r="I9" s="0">
         <v>0</v>
@@ -579,25 +579,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>209709789944</v>
+        <v>4153440</v>
       </c>
       <c r="C10" s="0">
-        <v>36312676120</v>
+        <v>2418546</v>
       </c>
       <c r="D10" s="0">
-        <v>52580755021760</v>
+        <v>2195236107</v>
       </c>
       <c r="E10" s="0">
-        <v>0</v>
+        <v>3624255940</v>
       </c>
       <c r="F10" s="0">
-        <v>24271853062</v>
+        <v>286690383</v>
       </c>
       <c r="G10" s="0">
-        <v>58516020615256</v>
+        <v>266335365807</v>
       </c>
       <c r="H10" s="0">
-        <v>49049505207880</v>
+        <v>359690208597</v>
       </c>
       <c r="I10" s="0">
         <v>0</v>
@@ -620,25 +620,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>209709789944</v>
+        <v>4053676</v>
       </c>
       <c r="C11" s="0">
-        <v>36312676120</v>
+        <v>2360770</v>
       </c>
       <c r="D11" s="0">
-        <v>52580755021760</v>
+        <v>2350180323</v>
       </c>
       <c r="E11" s="0">
-        <v>0</v>
+        <v>4914157180</v>
       </c>
       <c r="F11" s="0">
-        <v>28055377973</v>
+        <v>270274653</v>
       </c>
       <c r="G11" s="0">
-        <v>58516020615256</v>
+        <v>222287845644</v>
       </c>
       <c r="H11" s="0">
-        <v>38753322359608</v>
+        <v>360643174959</v>
       </c>
       <c r="I11" s="0">
         <v>0</v>
@@ -661,13 +661,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>209709789944</v>
+        <v>4153440</v>
       </c>
       <c r="C12" s="0">
         <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>52580755021760</v>
+        <v>3041264424</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>37940819170432</v>
+        <v>568977689016</v>
       </c>
       <c r="H12" s="0">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>209709789944</v>
+        <v>3778918</v>
       </c>
       <c r="C13" s="0">
         <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>52580755021760</v>
+        <v>2746754628</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>35145643233776</v>
+        <v>534961293480</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>209709789944</v>
+        <v>4153440</v>
       </c>
       <c r="C14" s="0">
         <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>52580755021760</v>
+        <v>1202570160</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <v>40624187304904</v>
+        <v>261156261411</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>209709789944</v>
+        <v>3778918</v>
       </c>
       <c r="C15" s="0">
         <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>52580755021760</v>
+        <v>4416264996</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>40624187304904</v>
+        <v>222287845644</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>209709789944</v>
+        <v>4053676</v>
       </c>
       <c r="C16" s="0">
         <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>52580755021760</v>
+        <v>2246829234</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>37940819170432</v>
+        <v>406774069173</v>
       </c>
       <c r="H16" s="0">
         <v>0</v>
@@ -866,13 +866,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>209709789944</v>
+        <v>3552820</v>
       </c>
       <c r="C17" s="0">
         <v>0</v>
       </c>
       <c r="D17" s="0">
-        <v>52580755021760</v>
+        <v>1639565974</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="0">
-        <v>40652242682877</v>
+        <v>535527510996</v>
       </c>
       <c r="H17" s="0">
         <v>0</v>
@@ -907,13 +907,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>209709789944</v>
+        <v>4053676</v>
       </c>
       <c r="C18" s="0">
         <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>52580755021760</v>
+        <v>4777929288</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>49134836645728</v>
+        <v>266335365807</v>
       </c>
       <c r="H18" s="0">
         <v>0</v>
@@ -948,13 +948,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>209709789944</v>
+        <v>3312010</v>
       </c>
       <c r="C19" s="0">
         <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>52580755021760</v>
+        <v>2195236107</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>49134836645728</v>
+        <v>189228174408</v>
       </c>
       <c r="H19" s="0">
         <v>0</v>
@@ -989,13 +989,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>209709789944</v>
+        <v>3552820</v>
       </c>
       <c r="C20" s="0">
         <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>52580755021760</v>
+        <v>1923117300</v>
       </c>
       <c r="E20" s="0">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <v>35145643233776</v>
+        <v>423462249270</v>
       </c>
       <c r="H20" s="0">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>209709789944</v>
+        <v>2710688</v>
       </c>
       <c r="C21" s="0">
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>52580755021760</v>
+        <v>4776729975</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>40624187304904</v>
+        <v>592947309768</v>
       </c>
       <c r="H21" s="0">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>52580755021760</v>
+        <v>4305519162</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="0">
-        <v>52580755021760</v>
+        <v>1639565974</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>52580755021760</v>
+        <v>3499636062</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>52580755021760</v>
+        <v>2246829234</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>52580755021760</v>
+        <v>1923117300</v>
       </c>
       <c r="E26" s="0">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>52580755021760</v>
+        <v>3499636062</v>
       </c>
       <c r="E27" s="0">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>52580755021760</v>
+        <v>4416264996</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>52580755021760</v>
+        <v>1923117300</v>
       </c>
       <c r="E29" s="0">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>52580755021760</v>
+        <v>3416034190</v>
       </c>
       <c r="E30" s="0">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>52580755021760</v>
+        <v>4777929288</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>
